--- a/server/data.xlsx
+++ b/server/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Documents\project\bunker-online\server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AC6155-3935-46D9-98DB-B07E724E06BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2AC275-F61B-4C0B-A2BC-A6FFDD153099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Характеристики" sheetId="1" r:id="rId1"/>
@@ -2347,14 +2347,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I429"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="10.58203125" customWidth="1"/>
+    <col min="2" max="2" width="16.375" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2383,7 +2383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -2586,7 +2586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -2702,7 +2702,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -2731,7 +2731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -2847,7 +2847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -2963,7 +2963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -3166,7 +3166,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -3369,7 +3369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -3398,7 +3398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -3456,7 +3456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -3557,7 +3557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -3586,7 +3586,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>5</v>
       </c>
@@ -3702,7 +3702,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -3731,7 +3731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -3760,7 +3760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>5</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>5</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>5</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>5</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>5</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>5</v>
       </c>
@@ -3963,7 +3963,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>5</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>5</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>5</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>5</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>5</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>5</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>5</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>5</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>5</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>5</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>5</v>
       </c>
@@ -4311,7 +4311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>5</v>
       </c>
@@ -4340,7 +4340,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>5</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>5</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>5</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>5</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>5</v>
       </c>
@@ -4485,7 +4485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>5</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>5</v>
       </c>
@@ -4540,7 +4540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>5</v>
       </c>
@@ -4569,7 +4569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>5</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>5</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>5</v>
       </c>
@@ -4656,7 +4656,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>5</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>5</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>5</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>5</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>5</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>5</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>5</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>5</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -4946,7 +4946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>5</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -5004,7 +5004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -5033,7 +5033,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -5062,7 +5062,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>95</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>95</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>95</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>95</v>
       </c>
@@ -5178,7 +5178,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>95</v>
       </c>
@@ -5207,7 +5207,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>95</v>
       </c>
@@ -5236,7 +5236,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>95</v>
       </c>
@@ -5265,7 +5265,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>95</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>95</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>95</v>
       </c>
@@ -5352,7 +5352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>95</v>
       </c>
@@ -5381,7 +5381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>95</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>95</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>95</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>95</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>95</v>
       </c>
@@ -5526,7 +5526,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>95</v>
       </c>
@@ -5555,7 +5555,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>95</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>95</v>
       </c>
@@ -5613,7 +5613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>95</v>
       </c>
@@ -5642,7 +5642,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>95</v>
       </c>
@@ -5671,7 +5671,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>95</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>95</v>
       </c>
@@ -5729,7 +5729,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>95</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>95</v>
       </c>
@@ -5787,7 +5787,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>95</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>95</v>
       </c>
@@ -5845,7 +5845,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>95</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>95</v>
       </c>
@@ -5903,7 +5903,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>95</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>95</v>
       </c>
@@ -5961,7 +5961,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>95</v>
       </c>
@@ -5990,7 +5990,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>95</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>95</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>95</v>
       </c>
@@ -6077,7 +6077,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>95</v>
       </c>
@@ -6106,7 +6106,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>95</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>95</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>95</v>
       </c>
@@ -6193,7 +6193,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>95</v>
       </c>
@@ -6222,7 +6222,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>95</v>
       </c>
@@ -6251,7 +6251,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>95</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>95</v>
       </c>
@@ -6309,7 +6309,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>95</v>
       </c>
@@ -6338,7 +6338,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>95</v>
       </c>
@@ -6367,7 +6367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>95</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>95</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>95</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>95</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>95</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>95</v>
       </c>
@@ -6541,7 +6541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>95</v>
       </c>
@@ -6570,7 +6570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>95</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>95</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>95</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>95</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>158</v>
       </c>
@@ -6709,7 +6709,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>158</v>
       </c>
@@ -6738,7 +6738,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>158</v>
       </c>
@@ -6767,7 +6767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>158</v>
       </c>
@@ -6796,7 +6796,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>158</v>
       </c>
@@ -6825,7 +6825,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>170</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>170</v>
       </c>
@@ -6883,7 +6883,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>170</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>170</v>
       </c>
@@ -6941,7 +6941,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>170</v>
       </c>
@@ -6970,7 +6970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>170</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>170</v>
       </c>
@@ -7028,7 +7028,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>170</v>
       </c>
@@ -7057,7 +7057,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>170</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>170</v>
       </c>
@@ -7115,7 +7115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>170</v>
       </c>
@@ -7144,7 +7144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>170</v>
       </c>
@@ -7173,7 +7173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>170</v>
       </c>
@@ -7202,7 +7202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>170</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>170</v>
       </c>
@@ -7260,7 +7260,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>170</v>
       </c>
@@ -7289,7 +7289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>170</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>170</v>
       </c>
@@ -7347,7 +7347,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>170</v>
       </c>
@@ -7376,7 +7376,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>170</v>
       </c>
@@ -7405,7 +7405,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>170</v>
       </c>
@@ -7434,7 +7434,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>170</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>170</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>170</v>
       </c>
@@ -7521,7 +7521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>170</v>
       </c>
@@ -7550,7 +7550,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>170</v>
       </c>
@@ -7579,7 +7579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>170</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>170</v>
       </c>
@@ -7637,7 +7637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>170</v>
       </c>
@@ -7666,7 +7666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>170</v>
       </c>
@@ -7695,7 +7695,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>170</v>
       </c>
@@ -7724,7 +7724,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>170</v>
       </c>
@@ -7753,7 +7753,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>170</v>
       </c>
@@ -7782,7 +7782,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>170</v>
       </c>
@@ -7811,7 +7811,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>170</v>
       </c>
@@ -7840,7 +7840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>170</v>
       </c>
@@ -7869,7 +7869,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>170</v>
       </c>
@@ -7898,7 +7898,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>170</v>
       </c>
@@ -7927,7 +7927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>170</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>170</v>
       </c>
@@ -7985,7 +7985,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>170</v>
       </c>
@@ -8014,7 +8014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>170</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>170</v>
       </c>
@@ -8072,7 +8072,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>170</v>
       </c>
@@ -8101,7 +8101,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>170</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>170</v>
       </c>
@@ -8159,7 +8159,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>170</v>
       </c>
@@ -8188,7 +8188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>170</v>
       </c>
@@ -8217,7 +8217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>170</v>
       </c>
@@ -8246,7 +8246,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>170</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>170</v>
       </c>
@@ -8304,7 +8304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>170</v>
       </c>
@@ -8333,7 +8333,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>170</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>170</v>
       </c>
@@ -8391,7 +8391,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>170</v>
       </c>
@@ -8420,7 +8420,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>170</v>
       </c>
@@ -8449,7 +8449,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>170</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>170</v>
       </c>
@@ -8507,7 +8507,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>170</v>
       </c>
@@ -8536,7 +8536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>170</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>233</v>
       </c>
@@ -8594,7 +8594,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>233</v>
       </c>
@@ -8623,7 +8623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>233</v>
       </c>
@@ -8652,7 +8652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>233</v>
       </c>
@@ -8681,7 +8681,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>233</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>233</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>233</v>
       </c>
@@ -8768,7 +8768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>233</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>233</v>
       </c>
@@ -8826,7 +8826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>233</v>
       </c>
@@ -8855,7 +8855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>233</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>233</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>233</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>233</v>
       </c>
@@ -8971,7 +8971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>233</v>
       </c>
@@ -9000,7 +9000,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>233</v>
       </c>
@@ -9029,7 +9029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>233</v>
       </c>
@@ -9058,7 +9058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>233</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>233</v>
       </c>
@@ -9116,7 +9116,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>233</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="236" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>233</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>233</v>
       </c>
@@ -9203,7 +9203,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>233</v>
       </c>
@@ -9232,7 +9232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>233</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>233</v>
       </c>
@@ -9290,7 +9290,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>233</v>
       </c>
@@ -9319,7 +9319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>233</v>
       </c>
@@ -9348,7 +9348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>233</v>
       </c>
@@ -9377,7 +9377,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="244" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>233</v>
       </c>
@@ -9406,7 +9406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="245" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>233</v>
       </c>
@@ -9435,7 +9435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="246" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>233</v>
       </c>
@@ -9464,7 +9464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>233</v>
       </c>
@@ -9493,7 +9493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>233</v>
       </c>
@@ -9522,7 +9522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>233</v>
       </c>
@@ -9551,7 +9551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="250" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>233</v>
       </c>
@@ -9580,7 +9580,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>233</v>
       </c>
@@ -9609,7 +9609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>233</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>233</v>
       </c>
@@ -9667,7 +9667,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>233</v>
       </c>
@@ -9696,7 +9696,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>233</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>233</v>
       </c>
@@ -9754,7 +9754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>233</v>
       </c>
@@ -9783,7 +9783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>233</v>
       </c>
@@ -9812,7 +9812,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>233</v>
       </c>
@@ -9841,7 +9841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>233</v>
       </c>
@@ -9870,7 +9870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>233</v>
       </c>
@@ -9899,7 +9899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>233</v>
       </c>
@@ -9928,7 +9928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>233</v>
       </c>
@@ -9957,7 +9957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>233</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>233</v>
       </c>
@@ -10015,7 +10015,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>233</v>
       </c>
@@ -10044,7 +10044,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="267" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>233</v>
       </c>
@@ -10073,7 +10073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="268" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>233</v>
       </c>
@@ -10102,7 +10102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="269" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>233</v>
       </c>
@@ -10131,7 +10131,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="270" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>233</v>
       </c>
@@ -10160,7 +10160,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="271" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>233</v>
       </c>
@@ -10189,7 +10189,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="272" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>233</v>
       </c>
@@ -10218,7 +10218,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="273" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>233</v>
       </c>
@@ -10247,7 +10247,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>233</v>
       </c>
@@ -10276,7 +10276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>233</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="276" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>233</v>
       </c>
@@ -10334,7 +10334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="277" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>233</v>
       </c>
@@ -10363,7 +10363,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>233</v>
       </c>
@@ -10392,7 +10392,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="279" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>233</v>
       </c>
@@ -10421,7 +10421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="280" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>233</v>
       </c>
@@ -10450,7 +10450,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>322</v>
       </c>
@@ -10479,7 +10479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>322</v>
       </c>
@@ -10508,7 +10508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>322</v>
       </c>
@@ -10537,7 +10537,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>322</v>
       </c>
@@ -10566,7 +10566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>322</v>
       </c>
@@ -10595,7 +10595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>322</v>
       </c>
@@ -10624,7 +10624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>322</v>
       </c>
@@ -10653,7 +10653,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>322</v>
       </c>
@@ -10682,7 +10682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>322</v>
       </c>
@@ -10711,7 +10711,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>322</v>
       </c>
@@ -10740,7 +10740,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>322</v>
       </c>
@@ -10769,7 +10769,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>322</v>
       </c>
@@ -10798,7 +10798,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>322</v>
       </c>
@@ -10827,7 +10827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>322</v>
       </c>
@@ -10856,7 +10856,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>322</v>
       </c>
@@ -10885,7 +10885,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>322</v>
       </c>
@@ -10914,7 +10914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>322</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>322</v>
       </c>
@@ -10972,7 +10972,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>322</v>
       </c>
@@ -11001,7 +11001,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>322</v>
       </c>
@@ -11030,7 +11030,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>322</v>
       </c>
@@ -11059,7 +11059,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>322</v>
       </c>
@@ -11088,7 +11088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>322</v>
       </c>
@@ -11117,7 +11117,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>322</v>
       </c>
@@ -11146,7 +11146,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>322</v>
       </c>
@@ -11175,7 +11175,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>322</v>
       </c>
@@ -11204,7 +11204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>322</v>
       </c>
@@ -11233,7 +11233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>322</v>
       </c>
@@ -11262,7 +11262,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>322</v>
       </c>
@@ -11291,7 +11291,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>322</v>
       </c>
@@ -11320,7 +11320,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="311" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>322</v>
       </c>
@@ -11349,7 +11349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="312" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>322</v>
       </c>
@@ -11378,7 +11378,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="313" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>322</v>
       </c>
@@ -11407,7 +11407,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="314" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>322</v>
       </c>
@@ -11436,7 +11436,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="315" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>322</v>
       </c>
@@ -11465,7 +11465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>322</v>
       </c>
@@ -11494,7 +11494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="317" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>322</v>
       </c>
@@ -11523,7 +11523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>322</v>
       </c>
@@ -11552,7 +11552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="319" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>322</v>
       </c>
@@ -11581,7 +11581,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>322</v>
       </c>
@@ -11610,7 +11610,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>322</v>
       </c>
@@ -11639,7 +11639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>322</v>
       </c>
@@ -11668,7 +11668,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>322</v>
       </c>
@@ -11697,7 +11697,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>322</v>
       </c>
@@ -11726,7 +11726,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>322</v>
       </c>
@@ -11755,7 +11755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>322</v>
       </c>
@@ -11784,7 +11784,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>322</v>
       </c>
@@ -11813,7 +11813,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="328" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>322</v>
       </c>
@@ -11842,7 +11842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="329" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>322</v>
       </c>
@@ -11871,7 +11871,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>322</v>
       </c>
@@ -11900,7 +11900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>322</v>
       </c>
@@ -11929,7 +11929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="332" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>322</v>
       </c>
@@ -11958,7 +11958,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="333" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>322</v>
       </c>
@@ -11987,7 +11987,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="334" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>322</v>
       </c>
@@ -12016,7 +12016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="335" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>322</v>
       </c>
@@ -12045,7 +12045,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="336" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>322</v>
       </c>
@@ -12074,7 +12074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="337" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>322</v>
       </c>
@@ -12103,7 +12103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="338" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>322</v>
       </c>
@@ -12132,7 +12132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>322</v>
       </c>
@@ -12161,7 +12161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>322</v>
       </c>
@@ -12190,7 +12190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>322</v>
       </c>
@@ -12219,7 +12219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="342" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>322</v>
       </c>
@@ -12248,7 +12248,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="343" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>322</v>
       </c>
@@ -12277,7 +12277,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="344" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>322</v>
       </c>
@@ -12306,7 +12306,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="345" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>322</v>
       </c>
@@ -12335,7 +12335,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="346" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>322</v>
       </c>
@@ -12364,7 +12364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="347" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>322</v>
       </c>
@@ -12393,7 +12393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="348" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>322</v>
       </c>
@@ -12422,7 +12422,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="349" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>322</v>
       </c>
@@ -12451,7 +12451,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="350" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>322</v>
       </c>
@@ -12480,7 +12480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="351" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>322</v>
       </c>
@@ -12509,7 +12509,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="352" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>322</v>
       </c>
@@ -12538,7 +12538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="353" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>322</v>
       </c>
@@ -12567,7 +12567,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="354" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>322</v>
       </c>
@@ -12596,7 +12596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="355" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>322</v>
       </c>
@@ -12625,7 +12625,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="356" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>322</v>
       </c>
@@ -12654,7 +12654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="357" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>322</v>
       </c>
@@ -12683,7 +12683,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="358" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>322</v>
       </c>
@@ -12712,7 +12712,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="359" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>322</v>
       </c>
@@ -12741,7 +12741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="360" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>322</v>
       </c>
@@ -12770,7 +12770,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>322</v>
       </c>
@@ -12799,7 +12799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="362" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>322</v>
       </c>
@@ -12828,7 +12828,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="363" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>322</v>
       </c>
@@ -12857,7 +12857,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="364" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>322</v>
       </c>
@@ -12886,7 +12886,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="365" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>322</v>
       </c>
@@ -12915,7 +12915,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="366" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>322</v>
       </c>
@@ -12944,7 +12944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="367" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>322</v>
       </c>
@@ -12973,7 +12973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="368" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>322</v>
       </c>
@@ -13002,7 +13002,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="369" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>322</v>
       </c>
@@ -13031,7 +13031,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="370" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>322</v>
       </c>
@@ -13060,7 +13060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="371" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>414</v>
       </c>
@@ -13089,7 +13089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="372" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>414</v>
       </c>
@@ -13118,7 +13118,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="373" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>414</v>
       </c>
@@ -13147,7 +13147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="374" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>414</v>
       </c>
@@ -13176,7 +13176,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="375" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>414</v>
       </c>
@@ -13205,7 +13205,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="376" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>414</v>
       </c>
@@ -13234,7 +13234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="377" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>414</v>
       </c>
@@ -13263,7 +13263,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="378" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>414</v>
       </c>
@@ -13292,7 +13292,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="379" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>414</v>
       </c>
@@ -13321,7 +13321,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="380" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>414</v>
       </c>
@@ -13350,7 +13350,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="381" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>414</v>
       </c>
@@ -13379,7 +13379,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="382" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>414</v>
       </c>
@@ -13408,7 +13408,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="383" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>414</v>
       </c>
@@ -13437,7 +13437,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="384" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>414</v>
       </c>
@@ -13466,7 +13466,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="385" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>414</v>
       </c>
@@ -13495,7 +13495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="386" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>414</v>
       </c>
@@ -13524,7 +13524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="387" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>414</v>
       </c>
@@ -13553,7 +13553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="388" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>414</v>
       </c>
@@ -13582,7 +13582,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="389" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>414</v>
       </c>
@@ -13611,7 +13611,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="390" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>414</v>
       </c>
@@ -13640,7 +13640,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="391" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>414</v>
       </c>
@@ -13669,7 +13669,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="392" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>414</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="393" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>414</v>
       </c>
@@ -13727,7 +13727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="394" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>414</v>
       </c>
@@ -13756,7 +13756,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="395" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>414</v>
       </c>
@@ -13785,7 +13785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="396" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>414</v>
       </c>
@@ -13814,7 +13814,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="397" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>414</v>
       </c>
@@ -13843,7 +13843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="398" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>414</v>
       </c>
@@ -13872,7 +13872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="399" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>414</v>
       </c>
@@ -13901,7 +13901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="400" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>414</v>
       </c>
@@ -13930,7 +13930,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="401" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>414</v>
       </c>
@@ -13959,7 +13959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="402" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>414</v>
       </c>
@@ -13988,7 +13988,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="403" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>414</v>
       </c>
@@ -14017,7 +14017,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="404" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>414</v>
       </c>
@@ -14046,7 +14046,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="405" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>414</v>
       </c>
@@ -14075,7 +14075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="406" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>414</v>
       </c>
@@ -14104,7 +14104,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="407" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>414</v>
       </c>
@@ -14133,7 +14133,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="408" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>414</v>
       </c>
@@ -14162,7 +14162,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="409" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>414</v>
       </c>
@@ -14191,7 +14191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="410" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>414</v>
       </c>
@@ -14220,7 +14220,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="411" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>414</v>
       </c>
@@ -14249,7 +14249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="412" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>414</v>
       </c>
@@ -14278,7 +14278,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="413" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>414</v>
       </c>
@@ -14307,7 +14307,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="414" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>414</v>
       </c>
@@ -14336,7 +14336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="415" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>414</v>
       </c>
@@ -14365,7 +14365,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="416" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>414</v>
       </c>
@@ -14394,7 +14394,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="417" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>414</v>
       </c>
@@ -14423,7 +14423,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="418" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>414</v>
       </c>
@@ -14452,7 +14452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="419" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>414</v>
       </c>
@@ -14481,7 +14481,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="420" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>414</v>
       </c>
@@ -14510,7 +14510,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="421" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>414</v>
       </c>
@@ -14539,7 +14539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="422" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>414</v>
       </c>
@@ -14568,7 +14568,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="423" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>414</v>
       </c>
@@ -14597,7 +14597,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="424" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>414</v>
       </c>
@@ -14626,7 +14626,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="425" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>414</v>
       </c>
@@ -14655,7 +14655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="426" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>414</v>
       </c>
@@ -14684,7 +14684,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="427" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>414</v>
       </c>
@@ -14713,7 +14713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="428" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>414</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="429" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>414</v>
       </c>
@@ -14791,9 +14791,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R32"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>477</v>
       </c>
@@ -14849,7 +14849,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>495</v>
       </c>
@@ -14887,16 +14887,16 @@
         <v>0.85</v>
       </c>
       <c r="M2">
+        <v>0.4</v>
+      </c>
+      <c r="N2">
         <v>0.3</v>
       </c>
-      <c r="N2">
-        <v>0.2</v>
-      </c>
       <c r="O2">
+        <v>0.25</v>
+      </c>
+      <c r="P2">
         <v>0.15</v>
-      </c>
-      <c r="P2">
-        <v>0.1</v>
       </c>
       <c r="Q2">
         <v>0.05</v>
@@ -14905,7 +14905,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>503</v>
       </c>
@@ -14943,16 +14943,16 @@
         <v>0.85</v>
       </c>
       <c r="M3">
+        <v>0.4</v>
+      </c>
+      <c r="N3">
         <v>0.3</v>
       </c>
-      <c r="N3">
-        <v>0.2</v>
-      </c>
       <c r="O3">
+        <v>0.25</v>
+      </c>
+      <c r="P3">
         <v>0.15</v>
-      </c>
-      <c r="P3">
-        <v>0.1</v>
       </c>
       <c r="Q3">
         <v>0.05</v>
@@ -14961,7 +14961,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>510</v>
       </c>
@@ -14999,16 +14999,16 @@
         <v>0.85</v>
       </c>
       <c r="M4">
+        <v>0.4</v>
+      </c>
+      <c r="N4">
         <v>0.3</v>
       </c>
-      <c r="N4">
-        <v>0.2</v>
-      </c>
       <c r="O4">
+        <v>0.25</v>
+      </c>
+      <c r="P4">
         <v>0.15</v>
-      </c>
-      <c r="P4">
-        <v>0.1</v>
       </c>
       <c r="Q4">
         <v>0.05</v>
@@ -15017,7 +15017,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>514</v>
       </c>
@@ -15055,16 +15055,16 @@
         <v>0.85</v>
       </c>
       <c r="M5">
+        <v>0.4</v>
+      </c>
+      <c r="N5">
         <v>0.3</v>
       </c>
-      <c r="N5">
-        <v>0.2</v>
-      </c>
       <c r="O5">
+        <v>0.25</v>
+      </c>
+      <c r="P5">
         <v>0.15</v>
-      </c>
-      <c r="P5">
-        <v>0.1</v>
       </c>
       <c r="Q5">
         <v>0.05</v>
@@ -15073,7 +15073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>518</v>
       </c>
@@ -15111,16 +15111,16 @@
         <v>0.85</v>
       </c>
       <c r="M6">
+        <v>0.4</v>
+      </c>
+      <c r="N6">
         <v>0.3</v>
       </c>
-      <c r="N6">
-        <v>0.2</v>
-      </c>
       <c r="O6">
+        <v>0.25</v>
+      </c>
+      <c r="P6">
         <v>0.15</v>
-      </c>
-      <c r="P6">
-        <v>0.1</v>
       </c>
       <c r="Q6">
         <v>0.05</v>
@@ -15129,7 +15129,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>522</v>
       </c>
@@ -15167,16 +15167,16 @@
         <v>0.85</v>
       </c>
       <c r="M7">
+        <v>0.4</v>
+      </c>
+      <c r="N7">
         <v>0.3</v>
       </c>
-      <c r="N7">
-        <v>0.2</v>
-      </c>
       <c r="O7">
+        <v>0.25</v>
+      </c>
+      <c r="P7">
         <v>0.15</v>
-      </c>
-      <c r="P7">
-        <v>0.1</v>
       </c>
       <c r="Q7">
         <v>0.05</v>
@@ -15185,7 +15185,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>526</v>
       </c>
@@ -15223,7 +15223,7 @@
         <v>0.15</v>
       </c>
       <c r="M8">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="N8">
         <v>0.4</v>
@@ -15241,7 +15241,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>531</v>
       </c>
@@ -15279,7 +15279,7 @@
         <v>0.15</v>
       </c>
       <c r="M9">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="N9">
         <v>0.4</v>
@@ -15297,7 +15297,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>532</v>
       </c>
@@ -15335,7 +15335,7 @@
         <v>0.15</v>
       </c>
       <c r="M10">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="N10">
         <v>0.4</v>
@@ -15353,7 +15353,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>537</v>
       </c>
@@ -15391,7 +15391,7 @@
         <v>0.15</v>
       </c>
       <c r="M11">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="N11">
         <v>0.4</v>
@@ -15409,7 +15409,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>540</v>
       </c>
@@ -15447,7 +15447,7 @@
         <v>0.15</v>
       </c>
       <c r="M12">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="N12">
         <v>0.4</v>
@@ -15465,7 +15465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>544</v>
       </c>
@@ -15503,7 +15503,7 @@
         <v>0.15</v>
       </c>
       <c r="M13">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="N13">
         <v>0.4</v>
@@ -15521,7 +15521,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>550</v>
       </c>
@@ -15559,7 +15559,7 @@
         <v>0.15</v>
       </c>
       <c r="M14">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="N14">
         <v>0.4</v>
@@ -15577,7 +15577,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>555</v>
       </c>
@@ -15624,7 +15624,7 @@
         <v>0.35</v>
       </c>
       <c r="P15">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Q15">
         <v>0.75</v>
@@ -15633,7 +15633,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>560</v>
       </c>
@@ -15680,7 +15680,7 @@
         <v>0.35</v>
       </c>
       <c r="P16">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Q16">
         <v>0.75</v>
@@ -15689,7 +15689,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>561</v>
       </c>
@@ -15736,7 +15736,7 @@
         <v>0.35</v>
       </c>
       <c r="P17">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Q17">
         <v>0.75</v>
@@ -15745,7 +15745,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>567</v>
       </c>
@@ -15792,7 +15792,7 @@
         <v>0.35</v>
       </c>
       <c r="P18">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Q18">
         <v>0.75</v>
@@ -15801,7 +15801,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>572</v>
       </c>
@@ -15848,7 +15848,7 @@
         <v>0.35</v>
       </c>
       <c r="P19">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Q19">
         <v>0.75</v>
@@ -15857,7 +15857,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>573</v>
       </c>
@@ -15904,7 +15904,7 @@
         <v>0.35</v>
       </c>
       <c r="P20">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Q20">
         <v>0.75</v>
@@ -15913,7 +15913,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>574</v>
       </c>
@@ -15960,7 +15960,7 @@
         <v>0.35</v>
       </c>
       <c r="P21">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Q21">
         <v>0.75</v>
@@ -15969,7 +15969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>575</v>
       </c>
@@ -16016,7 +16016,7 @@
         <v>0.35</v>
       </c>
       <c r="P22">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Q22">
         <v>0.75</v>
@@ -16025,7 +16025,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>581</v>
       </c>
@@ -16072,7 +16072,7 @@
         <v>0.35</v>
       </c>
       <c r="P23">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="Q23">
         <v>0.75</v>
@@ -16081,7 +16081,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>582</v>
       </c>
@@ -16119,13 +16119,13 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N24">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="O24">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="P24">
         <v>0.2</v>
@@ -16137,7 +16137,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>588</v>
       </c>
@@ -16175,13 +16175,13 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N25">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="O25">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="P25">
         <v>0.2</v>
@@ -16193,7 +16193,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>589</v>
       </c>
@@ -16231,13 +16231,13 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N26">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="O26">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="P26">
         <v>0.2</v>
@@ -16249,7 +16249,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>590</v>
       </c>
@@ -16287,13 +16287,13 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N27">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="O27">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="P27">
         <v>0.2</v>
@@ -16305,7 +16305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>593</v>
       </c>
@@ -16343,13 +16343,13 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N28">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="O28">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="P28">
         <v>0.2</v>
@@ -16361,7 +16361,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>597</v>
       </c>
@@ -16399,13 +16399,13 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N29">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="O29">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="P29">
         <v>0.2</v>
@@ -16417,7 +16417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>600</v>
       </c>
@@ -16455,13 +16455,13 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N30">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="O30">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="P30">
         <v>0.2</v>
@@ -16473,7 +16473,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>601</v>
       </c>
@@ -16511,13 +16511,13 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N31">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="O31">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="P31">
         <v>0.2</v>
@@ -16529,7 +16529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>605</v>
       </c>
@@ -16567,13 +16567,13 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N32">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="O32">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="P32">
         <v>0.2</v>
@@ -16588,7 +16588,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:R1 A25:B25 A8:K8 O8:R8 A9:K14 O9:R14 A15:L15 A16:L23 A24:B24 N24 A7:L7 O7:R7 A2:L6 O3:R6 N25:N32 A31:L32 A30:B30 D30:L30 A29:B29 D29:L29 A28:L28 A27:B27 D27:L27 A26:B26 D26:L26 D25:L25 D24:L24 R15 R16:R22 R24 R26:R32 O2:R2 R25 R23" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:R1 A25:B25 A8:K8 O8:R8 A9:K14 O9:R14 A15:L15 A16:L23 A24:B24 A7:L7 A2:L6 A31:L32 A30:B30 D30:L30 A29:B29 D29:L29 A28:L28 A27:B27 D27:L27 A26:B26 D26:L26 D25:L25 D24:L24 R15 R16:R22 R24 R26:R32 R25 R23 Q2:R2 Q7:R7 Q3:R6" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -16596,9 +16596,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>606</v>
       </c>
@@ -16606,7 +16606,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>606</v>
       </c>
@@ -16614,7 +16614,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>606</v>
       </c>
@@ -16622,7 +16622,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>606</v>
       </c>
@@ -16630,7 +16630,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>606</v>
       </c>
@@ -16638,7 +16638,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>606</v>
       </c>
@@ -16646,7 +16646,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>606</v>
       </c>
@@ -16654,7 +16654,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>606</v>
       </c>
@@ -16662,7 +16662,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>606</v>
       </c>
@@ -16670,7 +16670,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>606</v>
       </c>
@@ -16678,7 +16678,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>606</v>
       </c>
@@ -16686,7 +16686,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>606</v>
       </c>
@@ -16694,7 +16694,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>606</v>
       </c>
@@ -16702,7 +16702,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>606</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>606</v>
       </c>
@@ -16718,7 +16718,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>621</v>
       </c>
@@ -16726,7 +16726,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>621</v>
       </c>
@@ -16734,7 +16734,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>621</v>
       </c>
@@ -16742,7 +16742,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>621</v>
       </c>
@@ -16750,7 +16750,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>621</v>
       </c>
@@ -16758,7 +16758,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>621</v>
       </c>
@@ -16766,7 +16766,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>621</v>
       </c>
@@ -16774,7 +16774,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>621</v>
       </c>
@@ -16782,7 +16782,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>630</v>
       </c>
@@ -16790,7 +16790,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>630</v>
       </c>
@@ -16798,7 +16798,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>630</v>
       </c>
@@ -16806,7 +16806,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>630</v>
       </c>
@@ -16814,7 +16814,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>630</v>
       </c>
@@ -16822,7 +16822,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>630</v>
       </c>
@@ -16830,7 +16830,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>630</v>
       </c>
@@ -16838,7 +16838,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>630</v>
       </c>
@@ -16846,7 +16846,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>630</v>
       </c>
@@ -16854,7 +16854,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>630</v>
       </c>
@@ -16873,9 +16873,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I5"/>
-  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>478</v>
       </c>
@@ -16904,7 +16904,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>496</v>
       </c>
@@ -16933,7 +16933,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>527</v>
       </c>
@@ -16962,7 +16962,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>556</v>
       </c>
@@ -16991,7 +16991,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>583</v>
       </c>

--- a/server/data.xlsx
+++ b/server/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Documents\project\bunker-online\server\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3DE163-596A-4AAE-B4BC-65843CEB8B3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A56A8E73-85BB-4909-9AA0-D2266E735D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
